--- a/processed_ruby_restored_xlsx/sc132_凛２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc132_凛２：恋人化.ss.xlsx
@@ -838,7 +838,8 @@
       <c r="B25" s="1" t="inlineStr">
         <is>
           <t>「...We'll see the dagashi shop soon, but do you want
-to stop at the dagashi shop or go to the secret base？」</t>
+to stop at the dagashi shop or go to the secret
+base？」</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1345,9 +1346,9 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Even though I had been standing by the door the moment
-I got off the bus, Rin-chan had gotten off before
-that…</t>
+          <t>Even though I had been standing by the door the
+moment I got off the bus, Rin-chan had gotten off
+before that…</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1377,8 +1378,8 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>「…Somehow, whenever we come here Rin-chan always seems
-to wander off on her own.」</t>
+          <t>「…Somehow, whenever we come here Rin-chan always
+seems to wander off on her own.」</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1594,8 +1595,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>She's the most dependable at times like this, so I can
-leave things to her.</t>
+          <t>She's the most dependable at times like this, so I
+can leave things to her.</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1779,8 +1780,8 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>At that curious age, things adults see as trivial feel
-important to them.</t>
+          <t>At that curious age, things adults see as trivial
+feel important to them.</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1795,8 +1796,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>A long, sturdy branch would already be a magic wand or
-a holy sword... well, that's how it looks to them.</t>
+          <t>A long, sturdy branch would already be a magic wand
+or a holy sword... well, that's how it looks to them.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1967,8 +1968,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>She's like that when she carries snacks too—where does
-Rin-chan always hide them？</t>
+          <t>She's like that when she carries snacks too—where
+does Rin-chan always hide them？</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2122,8 +2123,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan was so focused on the box she dug up that she
-showed no sign of noticing me.</t>
+          <t>Rin-chan was so focused on the box she dug up that
+she showed no sign of noticing me.</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2154,8 +2155,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>She was probably doing it so she could put it back the
-same way when she buried it again.</t>
+          <t>She was probably doing it so she could put it back
+the same way when she buried it again.</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2459,8 +2460,8 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan tries to hide the box, but she's a little too
-slow.</t>
+          <t>Rin-chan tries to hide the box, but she's a little
+too slow.</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2869,7 +2870,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan and whiskey bonbons are like catnip to a cat.</t>
+          <t>Rin-chan and whiskey bonbons are like catnip to a
+cat.</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3054,8 +3056,8 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>...And as soon as I took it, I stood up and held it up
-over my head.</t>
+          <t>...And as soon as I took it, I stood up and held it
+up over my head.</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3223,8 +3225,8 @@
       <c r="B180" s="1" t="inlineStr">
         <is>
           <t>I bent at the waist, keeping my hands held up so the
-box wouldn't be taken from me, and tried to meet their
-gaze as much as possible.</t>
+box wouldn't be taken from me, and tried to meet
+their gaze as much as possible.</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3722,8 +3724,8 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>She must've been pretty wiped from running all excited
-like that.</t>
+          <t>She must've been pretty wiped from running all
+excited like that.</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3768,9 +3770,9 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>Seeing Rin-chan who looked terribly grumpy and utterly
-exhausted, Miru-chan was startled and called out to
-her.</t>
+          <t>Seeing Rin-chan who looked terribly grumpy and
+utterly exhausted, Miru-chan was startled and called
+out to her.</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3785,8 +3787,8 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>As expected, the one who's first to worry about her is
-Miru-chan.</t>
+          <t>As expected, the one who's first to worry about her
+is Miru-chan.</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -4241,9 +4243,9 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>Whatever words are used, it would end up sounding bad,
-so it's a considerate move to avoid letting Rin‑chan
-hear.</t>
+          <t>Whatever words are used, it would end up sounding
+bad, so it's a considerate move to avoid letting
+Rin‑chan hear.</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4411,8 +4413,8 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>There’s only so much I can do now that I’ve become the
-villain in Rin-chan’s eyes.</t>
+          <t>There’s only so much I can do now that I’ve become
+the villain in Rin-chan’s eyes.</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4488,8 +4490,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>I tried to lure her with food and made a hamburg-steak
-Rin-chan special, but she turned away.</t>
+          <t>I tried to lure her with food and made a
+hamburg-steak Rin-chan special, but she turned away.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4855,8 +4857,9 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>...Rin-chan, without even saying 'itadakimasu,' starts
-eating the special hamburger with a sullen face.</t>
+          <t>...Rin-chan, without even saying 'itadakimasu,'
+starts eating the special hamburger with a sullen
+face.</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4947,8 +4950,8 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>…After dinner, I gathered everyone's dishes and got up
-from the table to clean up.</t>
+          <t>…After dinner, I gathered everyone's dishes and got
+up from the table to clean up.</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -5376,8 +5379,8 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>…No matter how I knocked or kept calling, there was no
-answer.</t>
+          <t>…No matter how I knocked or kept calling, there was
+no answer.</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -6236,8 +6239,8 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>The only thing that worries me is going out without my
-phone... I'll deal with that when the time comes.</t>
+          <t>The only thing that worries me is going out without
+my phone... I'll deal with that when the time comes.</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6433,8 +6436,8 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>I say it out loud as I sort through the information in
-my head.</t>
+          <t>I say it out loud as I sort through the information
+in my head.</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -6631,8 +6634,8 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>She says it firmly, and Rurichiyo-chan gives me a push
-of encouragement.</t>
+          <t>She says it firmly, and Rurichiyo-chan gives me a
+push of encouragement.</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6966,9 +6969,9 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>Being in a spot hemmed in on three sides by rock walls
-and with not a single streetlight—really, is it this
-dark...?</t>
+          <t>Being in a spot hemmed in on three sides by rock
+walls and with not a single streetlight—really, is it
+this dark...?</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -7015,8 +7018,8 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>If that's the case, that's fine, but I can't just stop
-searching halfway.</t>
+          <t>If that's the case, that's fine, but I can't just
+stop searching halfway.</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7076,7 +7079,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>We rounded the waterline and slipped into the grass...</t>
+          <t>We rounded the waterline and slipped into the
+grass...</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7410,8 +7414,8 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t>When I then ruffled her hair, Rin-chan exploded all at
-once.</t>
+          <t>When I then ruffled her hair, Rin-chan exploded all
+at once.</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7637,8 +7641,8 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>I couldn't tell the time, but after a little while Rin
-stopped choking.</t>
+          <t>I couldn't tell the time, but after a little while
+Rin stopped choking.</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7835,7 +7839,8 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>Smiling at Rin-chan like that, I went back to the bus.</t>
+          <t>Smiling at Rin-chan like that, I went back to the
+bus.</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7881,8 +7886,8 @@
       <c r="B485" s="1" t="inlineStr">
         <is>
           <t>Since I'd snuck out without Miru-chan and Nono-chan
-knowing, I stepped through the front door, making only
-a small sound.</t>
+knowing, I stepped through the front door, making
+only a small sound.</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -8111,8 +8116,8 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan smiles kindly at Rin-chan, and then she
-makes a surprised face.</t>
+          <t>Rurichiyo-chan smiles kindly at Rin-chan, and then
+she makes a surprised face.</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -8436,8 +8441,8 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>I watched Rin-chan and the others leave, and once they
-were out of sight I let out a big sigh.</t>
+          <t>I watched Rin-chan and the others leave, and once
+they were out of sight I let out a big sigh.</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -9646,8 +9651,8 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>With the way I said that just now, does that mean it's
-okay to eat it？</t>
+          <t>With the way I said that just now, does that mean
+it's okay to eat it？</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -9813,8 +9818,8 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan widened her eyes for a moment and then gave a
-big nod.</t>
+          <t>Rin-chan widened her eyes for a moment and then gave
+a big nod.</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -10731,8 +10736,8 @@
       <c r="B671" s="1" t="inlineStr">
         <is>
           <t>…I couldn't tell if I was gently prompting or
-deliberately teasing, and my voice ended up landing on
-a fine, ambiguous line.</t>
+deliberately teasing, and my voice ended up landing
+on a fine, ambiguous line.</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -10884,8 +10889,8 @@
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>Once she looks away, our conversation fizzles out even
-more because she's naturally quiet.</t>
+          <t>Once she looks away, our conversation fizzles out
+even more because she's naturally quiet.</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -10916,8 +10921,9 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>Trying to convince myself and staying silent, Rin-chan
-starts fidgeting with her hands under the futon.</t>
+          <t>Trying to convince myself and staying silent,
+Rin-chan starts fidgeting with her hands under the
+futon.</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -11007,7 +11013,8 @@
       </c>
       <c r="B689" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan grips my hand tightly and hesitates to speak.</t>
+          <t>Rin-chan grips my hand tightly and hesitates to
+speak.</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -11294,8 +11301,8 @@
       </c>
       <c r="B708" s="1" t="inlineStr">
         <is>
-          <t>I held back the heat in my chest and forced myself not
-to move.</t>
+          <t>I held back the heat in my chest and forced myself
+not to move.</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -12037,8 +12044,8 @@
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t>But now that her usual sass and shy fear are gone, all
-that's left is an age-appropriate cuteness.</t>
+          <t>But now that her usual sass and shy fear are gone,
+all that's left is an age-appropriate cuteness.</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -12098,8 +12105,8 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>Watching Rin-chan's sleeping face alone makes my heart
-feel happy.</t>
+          <t>Watching Rin-chan's sleeping face alone makes my
+heart feel happy.</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -12392,8 +12399,8 @@
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>But I have to work, and for other reasons I can't just
-do that.</t>
+          <t>But I have to work, and for other reasons I can't
+just do that.</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -12408,8 +12415,8 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>For example, if I slept with her until she woke up and
-we were late getting ready, people would ask why.</t>
+          <t>For example, if I slept with her until she woke up
+and we were late getting ready, people would ask why.</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12883,8 +12890,8 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan came into the living room a little later than
-everyone else.</t>
+          <t>Rin-chan came into the living room a little later
+than everyone else.</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -13235,8 +13242,8 @@
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>She must be thinking, better not say anything extra...
-or something like that.</t>
+          <t>She must be thinking, better not say anything
+extra... or something like that.</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -13480,8 +13487,8 @@
       </c>
       <c r="B851" s="1" t="inlineStr">
         <is>
-          <t>Everyone's voice was gentle as they showed concern for
-Rin.</t>
+          <t>Everyone's voice was gentle as they showed concern
+for Rin.</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -13680,8 +13687,8 @@
       </c>
       <c r="B864" s="1" t="inlineStr">
         <is>
-          <t>「Well, a lot happened last night... she was completely
-exhausted, so I let her sleep in my room.」</t>
+          <t>「Well, a lot happened last night... she was
+completely exhausted, so I let her sleep in my room.」</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -14230,7 +14237,8 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>Thanks to Miru-chan clowning around, the flow changed.</t>
+          <t>Thanks to Miru-chan clowning around, the flow
+changed.</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -14719,8 +14727,8 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>Since we finished in the morning today, I went back to
-the dorm and had lunch.</t>
+          <t>Since we finished in the morning today, I went back
+to the dorm and had lunch.</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -14999,8 +15007,9 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>I was so happy someone spoke to me that I spun around,
-and the momentum made Rin-chan take a step back.</t>
+          <t>I was so happy someone spoke to me that I spun
+around, and the momentum made Rin-chan take a step
+back.</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -15106,8 +15115,8 @@
       </c>
       <c r="B957" s="1" t="inlineStr">
         <is>
-          <t>But a forgotten thing... it could wait until tomorrow,
-but a drive together might be nice too.</t>
+          <t>But a forgotten thing... it could wait until
+tomorrow, but a drive together might be nice too.</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -15213,9 +15222,9 @@
       </c>
       <c r="B964" s="1" t="inlineStr">
         <is>
-          <t>I’d planned to pull the bus up like in the morning and
-have her get on there, but Rin-chan runs to keep up
-behind me.</t>
+          <t>I’d planned to pull the bus up like in the morning
+and have her get on there, but Rin-chan runs to keep
+up behind me.</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -16127,8 +16136,8 @@
       </c>
       <c r="B1024" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan ran off, but would it be wrong to chase after
-her and ask...?</t>
+          <t>Rin-chan ran off, but would it be wrong to chase
+after her and ask...?</t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -16189,9 +16198,9 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>I flipped through the pages and searched for the words
-she had just written, and then I couldn't believe my
-eyes.</t>
+          <t>I flipped through the pages and searched for the
+words she had just written, and then I couldn't
+believe my eyes.</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -16434,8 +16443,8 @@
       </c>
       <c r="B1044" s="1" t="inlineStr">
         <is>
-          <t>Because she usually hides her feelings, seeing such an
-obvious reaction from her makes me really happy.</t>
+          <t>Because she usually hides her feelings, seeing such
+an obvious reaction from her makes me really happy.</t>
         </is>
       </c>
       <c r="C1044" t="n">
@@ -16754,7 +16763,8 @@
       </c>
       <c r="B1065" s="1" t="inlineStr">
         <is>
-          <t>But Rin-chan just stares at me without moving an inch.</t>
+          <t>But Rin-chan just stares at me without moving an
+inch.</t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -17259,7 +17269,8 @@
       </c>
       <c r="B1098" s="1" t="inlineStr">
         <is>
-          <t>If I don't look sharp and cool, Rin-chan will hate me.</t>
+          <t>If I don't look sharp and cool, Rin-chan will hate
+me.</t>
         </is>
       </c>
       <c r="C1098" t="n">
@@ -17773,8 +17784,8 @@
       </c>
       <c r="B1132" s="1" t="inlineStr">
         <is>
-          <t>Still, as I used gestures to buy time, Rin-chan made a
-throat sound.</t>
+          <t>Still, as I used gestures to buy time, Rin-chan made
+a throat sound.</t>
         </is>
       </c>
       <c r="C1132" t="n">
@@ -17894,7 +17905,8 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>Saved by that, I reset and straightened my expression.</t>
+          <t>Saved by that, I reset and straightened my
+expression.</t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -18488,9 +18500,9 @@
       </c>
       <c r="B1179" s="1" t="inlineStr">
         <is>
-          <t>If I stuck out my tongue, Rin-chan stuck hers out, and
-when I tangled my tongue with hers she returned it
-just as much.</t>
+          <t>If I stuck out my tongue, Rin-chan stuck hers out,
+and when I tangled my tongue with hers she returned
+it just as much.</t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -19436,8 +19448,8 @@
       </c>
       <c r="B1241" s="1" t="inlineStr">
         <is>
-          <t>Upon hearing 'sex', she finally seemed to grasp what I
-meant.</t>
+          <t>Upon hearing 'sex', she finally seemed to grasp what
+I meant.</t>
         </is>
       </c>
       <c r="C1241" t="n">
@@ -19848,8 +19860,8 @@
       </c>
       <c r="B1268" s="1" t="inlineStr">
         <is>
-          <t>「Ah... u... th-then, Niini, you have to take yours off
-too...！」</t>
+          <t>「Ah... u... th-then, Niini, you have to take yours
+off too...！」</t>
         </is>
       </c>
       <c r="C1268" t="n">
@@ -19909,8 +19921,8 @@
       </c>
       <c r="B1272" s="1" t="inlineStr">
         <is>
-          <t>I strip off my shirt, my pants, even my underwear, and
-Rin-chan's eyes go wide.</t>
+          <t>I strip off my shirt, my pants, even my underwear,
+and Rin-chan's eyes go wide.</t>
         </is>
       </c>
       <c r="C1272" t="n">
@@ -20184,8 +20196,8 @@
       </c>
       <c r="B1290" s="1" t="inlineStr">
         <is>
-          <t>「But if we stay this close, wouldn't that be even more
-embarrassing...？」</t>
+          <t>「But if we stay this close, wouldn't that be even
+more embarrassing...？」</t>
         </is>
       </c>
       <c r="C1290" t="n">
@@ -20875,8 +20887,8 @@
       </c>
       <c r="B1335" s="1" t="inlineStr">
         <is>
-          <t>And this time I take hold of Rin-chan's waist and pull
-her closer.</t>
+          <t>And this time I take hold of Rin-chan's waist and
+pull her closer.</t>
         </is>
       </c>
       <c r="C1335" t="n">
@@ -20937,8 +20949,8 @@
       </c>
       <c r="B1339" s="1" t="inlineStr">
         <is>
-          <t>To check the height and angle further, I press the tip
-of the penis against the center of her
+          <t>To check the height and angle further, I press the
+tip of the penis against the center of her
 between-the-legs.</t>
         </is>
       </c>
@@ -21031,8 +21043,8 @@
       </c>
       <c r="B1345" s="1" t="inlineStr">
         <is>
-          <t>「Ah…！ Niini’s ochi-nchin… are you going to put it into
-Rin’s between (my/her) legs…？」</t>
+          <t>「Ah…！ Niini’s ochi-nchin… are you going to put it
+into Rin’s between (my/her) legs…？」</t>
         </is>
       </c>
       <c r="C1345" t="n">
@@ -21094,8 +21106,8 @@
       <c r="B1349" s="1" t="inlineStr">
         <is>
           <t>By putting it into words and telling them, I want to
-lessen their anxiety even a little and make them focus
-only on their arousal.</t>
+lessen their anxiety even a little and make them
+focus only on their arousal.</t>
         </is>
       </c>
       <c r="C1349" t="n">
@@ -21261,8 +21273,8 @@
       </c>
       <c r="B1360" s="1" t="inlineStr">
         <is>
-          <t>In the dirty manga we all read, lines about it feeling
-good were everywhere, but in reality…</t>
+          <t>In the dirty manga we all read, lines about it
+feeling good were everywhere, but in reality…</t>
         </is>
       </c>
       <c r="C1360" t="n">
@@ -21443,8 +21455,8 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>I don't know if it'll go exactly as she expects, but I
-push my hips in as gently as I can.</t>
+          <t>I don't know if it'll go exactly as she expects, but
+I push my hips in as gently as I can.</t>
         </is>
       </c>
       <c r="C1372" t="n">
@@ -22099,7 +22111,8 @@
       </c>
       <c r="B1415" s="1" t="inlineStr">
         <is>
-          <t>When we do, our attention naturally turns to Rin-chan.</t>
+          <t>When we do, our attention naturally turns to
+Rin-chan.</t>
         </is>
       </c>
       <c r="C1415" t="n">
@@ -22693,7 +22706,8 @@
       <c r="B1454" s="1" t="inlineStr">
         <is>
           <t>It looks like she’s so embarrassed she’s peaked and
-kind of spaced out... like she just flew off a little.</t>
+kind of spaced out... like she just flew off a
+little.</t>
         </is>
       </c>
       <c r="C1454" t="n">
@@ -22753,8 +22767,8 @@
       </c>
       <c r="B1458" s="1" t="inlineStr">
         <is>
-          <t>Watching in disbelief, Rin-chan began to twitch as she
-exhaled sharply.</t>
+          <t>Watching in disbelief, Rin-chan began to twitch as
+she exhaled sharply.</t>
         </is>
       </c>
       <c r="C1458" t="n">
@@ -23015,7 +23029,8 @@
       </c>
       <c r="B1475" s="1" t="inlineStr">
         <is>
-          <t>The red streak flowing from between Rin-chan's legs...</t>
+          <t>The red streak flowing from between Rin-chan's
+legs...</t>
         </is>
       </c>
       <c r="C1475" t="n">
@@ -23045,8 +23060,8 @@
       </c>
       <c r="B1477" s="1" t="inlineStr">
         <is>
-          <t>I trembled with emotion as I saw and confirmed with my
-eyes that I had received Rin-chan's first.</t>
+          <t>I trembled with emotion as I saw and confirmed with
+my eyes that I had received Rin-chan's first.</t>
         </is>
       </c>
       <c r="C1477" t="n">
@@ -23138,8 +23153,8 @@
       </c>
       <c r="B1483" s="1" t="inlineStr">
         <is>
-          <t>It was still narrow, of course, but the stimulation on
-the most sensitive tip had eased a bit.</t>
+          <t>It was still narrow, of course, but the stimulation
+on the most sensitive tip had eased a bit.</t>
         </is>
       </c>
       <c r="C1483" t="n">
@@ -23411,7 +23426,8 @@
       </c>
       <c r="B1501" s="1" t="inlineStr">
         <is>
-          <t>She looks like it's painful even to put it into words.</t>
+          <t>She looks like it's painful even to put it into
+words.</t>
         </is>
       </c>
       <c r="C1501" t="n">
@@ -23427,7 +23443,8 @@
       <c r="B1502" s="1" t="inlineStr">
         <is>
           <t>But what’s a little different from before is that
-Rin-chan’s consciousness seems to have become clearer.</t>
+Rin-chan’s consciousness seems to have become
+clearer.</t>
         </is>
       </c>
       <c r="C1502" t="n">
@@ -23458,8 +23475,8 @@
       </c>
       <c r="B1504" s="1" t="inlineStr">
         <is>
-          <t>On the other hand, is it okay to think that, because I
-got past that point, things actually became easier？</t>
+          <t>On the other hand, is it okay to think that, because
+I got past that point, things actually became easier？</t>
         </is>
       </c>
       <c r="C1504" t="n">
@@ -23629,8 +23646,9 @@
       <c r="B1515" s="1" t="inlineStr">
         <is>
           <t>After she became aware that the penis was inside, she
-realized the sensations she was feeling within herself
-and probably became even more conscious of them.</t>
+realized the sensations she was feeling within
+herself and probably became even more conscious of
+them.</t>
         </is>
       </c>
       <c r="C1515" t="n">
@@ -23903,8 +23921,8 @@
       </c>
       <c r="B1533" s="1" t="inlineStr">
         <is>
-          <t>「Mm... well, it's because it's absolutely necessary to
-make Rin-chan feel good, you see.」</t>
+          <t>「Mm... well, it's because it's absolutely necessary
+to make Rin-chan feel good, you see.」</t>
         </is>
       </c>
       <c r="C1533" t="n">
@@ -24594,8 +24612,8 @@
       </c>
       <c r="B1578" s="1" t="inlineStr">
         <is>
-          <t>When I rock my penis deep inside, Rin-chan's reactions
-dull.</t>
+          <t>When I rock my penis deep inside, Rin-chan's
+reactions dull.</t>
         </is>
       </c>
       <c r="C1578" t="n">
@@ -24640,7 +24658,8 @@
       </c>
       <c r="B1581" s="1" t="inlineStr">
         <is>
-          <t>「If it feels like that now, it should be okay, right？」</t>
+          <t>「If it feels like that now, it should be okay,
+right？」</t>
         </is>
       </c>
       <c r="C1581" t="n">
@@ -24670,8 +24689,8 @@
       </c>
       <c r="B1583" s="1" t="inlineStr">
         <is>
-          <t>「Hah... yes. I'm fi,ne... my stomach's... clenching...
-it's getting stronger...」</t>
+          <t>「Hah... yes. I'm fi,ne... my stomach's...
+clenching... it's getting stronger...」</t>
         </is>
       </c>
       <c r="C1583" t="n">
@@ -24702,8 +24721,8 @@
       </c>
       <c r="B1585" s="1" t="inlineStr">
         <is>
-          <t>Would it be similar to the sensation of feeling my own
-penis throbbing？</t>
+          <t>Would it be similar to the sensation of feeling my
+own penis throbbing？</t>
         </is>
       </c>
       <c r="C1585" t="n">
@@ -25022,8 +25041,8 @@
       </c>
       <c r="B1606" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Niini, it feels good for you too？ Hehe... Rin's
-so happy...」</t>
+          <t>「Ah... Niini, it feels good for you too？ Hehe...
+Rin's so happy...」</t>
         </is>
       </c>
       <c r="C1606" t="n">
@@ -25970,8 +25989,9 @@
       </c>
       <c r="B1668" s="1" t="inlineStr">
         <is>
-          <t>Even so, that urgency seems to have stirred her shame,
-and her whole cunt ripples and tightens harder.</t>
+          <t>Even so, that urgency seems to have stirred her
+shame, and her whole cunt ripples and tightens
+harder.</t>
         </is>
       </c>
       <c r="C1668" t="n">
@@ -26138,8 +26158,8 @@
       <c r="B1679" s="1" t="inlineStr">
         <is>
           <t>A pleasurable electric current slipped beneath my
-groin, circled around my penis once, and climbed up to
-the head.</t>
+groin, circled around my penis once, and climbed up
+to the head.</t>
         </is>
       </c>
       <c r="C1679" t="n">
@@ -26230,8 +26250,9 @@
       </c>
       <c r="B1685" s="1" t="inlineStr">
         <is>
-          <t>I've already jumped the gun and can barely get it out;
-there's no room to respond to Rin-chan's confusion.</t>
+          <t>I've already jumped the gun and can barely get it
+out; there's no room to respond to Rin-chan's
+confusion.</t>
         </is>
       </c>
       <c r="C1685" t="n">
@@ -26382,9 +26403,9 @@
       </c>
       <c r="B1695" s="1" t="inlineStr">
         <is>
-          <t>Unable to hold it in, when ejaculation began, Rin-chan
-opened her eyes wide and shifted her gaze down toward
-between her legs.</t>
+          <t>Unable to hold it in, when ejaculation began,
+Rin-chan opened her eyes wide and shifted her gaze
+down toward between her legs.</t>
         </is>
       </c>
       <c r="C1695" t="n">
@@ -26674,8 +26695,8 @@
       </c>
       <c r="B1714" s="1" t="inlineStr">
         <is>
-          <t>When I said "I love you," her vaginal muscles clenched
-tightly around me.</t>
+          <t>When I said "I love you," her vaginal muscles
+clenched tightly around me.</t>
         </is>
       </c>
       <c r="C1714" t="n">
@@ -26750,8 +26771,8 @@
       </c>
       <c r="B1719" s="1" t="inlineStr">
         <is>
-          <t>When I said it again to try it, sure enough her vagina
-clenched.</t>
+          <t>When I said it again to try it, sure enough her
+vagina clenched.</t>
         </is>
       </c>
       <c r="C1719" t="n">
@@ -27055,9 +27076,9 @@
       </c>
       <c r="B1739" s="1" t="inlineStr">
         <is>
-          <t>To ejaculate inside a girl is something lovers do when
-they're feeling good, and something done when making a
-baby.</t>
+          <t>To ejaculate inside a girl is something lovers do
+when they're feeling good, and something done when
+making a baby.</t>
         </is>
       </c>
       <c r="C1739" t="n">
@@ -27073,7 +27094,8 @@
       <c r="B1740" s="1" t="inlineStr">
         <is>
           <t>No matter how you framed it, it was still an act of
-love, so there was no need for a probing conversation.</t>
+love, so there was no need for a probing
+conversation.</t>
         </is>
       </c>
       <c r="C1740" t="n">
@@ -27316,8 +27338,8 @@
       </c>
       <c r="B1756" s="1" t="inlineStr">
         <is>
-          <t>But then, all at once, I realized that it had been the
-right thing.</t>
+          <t>But then, all at once, I realized that it had been
+the right thing.</t>
         </is>
       </c>
       <c r="C1756" t="n">
@@ -27577,9 +27599,9 @@
       </c>
       <c r="B1773" s="1" t="inlineStr">
         <is>
-          <t>At first Nono-chan seemed pretty weak in the mornings,
-but she’s gotten pretty used to the rhythm of life
-here.</t>
+          <t>At first Nono-chan seemed pretty weak in the
+mornings, but she’s gotten pretty used to the rhythm
+of life here.</t>
         </is>
       </c>
       <c r="C1773" t="n">
@@ -27746,8 +27768,8 @@
       </c>
       <c r="B1784" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan had brought Rin-chan into the living room as
-if tugging her along.</t>
+          <t>Miru-chan had brought Rin-chan into the living room
+as if tugging her along.</t>
         </is>
       </c>
       <c r="C1784" t="n">
@@ -27809,8 +27831,8 @@
       </c>
       <c r="B1788" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan murmured, eyes wide, and I forced a wry
-smile in my head.</t>
+          <t>Rurichiyo-chan murmured, eyes wide, and I forced a
+wry smile in my head.</t>
         </is>
       </c>
       <c r="C1788" t="n">
@@ -27857,8 +27879,8 @@
       <c r="B1791" s="1" t="inlineStr">
         <is>
           <t>She seemed to like basking in that horny feeling, so
-she'd sneak out of her room late at night to come over
-and we'd been smooching.</t>
+she'd sneak out of her room late at night to come
+over and we'd been smooching.</t>
         </is>
       </c>
       <c r="C1791" t="n">
@@ -27982,7 +28004,8 @@
       </c>
       <c r="B1799" s="1" t="inlineStr">
         <is>
-          <t>「Ah... it's already the closing ceremony, isn't it...」</t>
+          <t>「Ah... it's already the closing ceremony, isn't
+it...」</t>
         </is>
       </c>
       <c r="C1799" t="n">
@@ -28122,7 +28145,8 @@
       <c r="B1808" s="1" t="inlineStr">
         <is>
           <t>That aside, Nono-chan suddenly switched into teacher
-mode, straightened her back, and puffed out her chest.</t>
+mode, straightened her back, and puffed out her
+chest.</t>
         </is>
       </c>
       <c r="C1808" t="n">
@@ -28152,8 +28176,8 @@
       </c>
       <c r="B1810" s="1" t="inlineStr">
         <is>
-          <t>「Okay everyone. Summer vacation is starting, but don't
-go overboard — make sure you study too！」</t>
+          <t>「Okay everyone. Summer vacation is starting, but
+don't go overboard — make sure you study too！」</t>
         </is>
       </c>
       <c r="C1810" t="n">
@@ -28213,8 +28237,9 @@
       </c>
       <c r="B1814" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan-sensei？ If you say that now, you won't have
-anything to say at the closing ceremony, you know？」</t>
+          <t>「Nono-chan-sensei？ If you say that now, you won't
+have anything to say at the closing ceremony, you
+know？」</t>
         </is>
       </c>
       <c r="C1814" t="n">
@@ -28810,7 +28835,8 @@
       <c r="B1853" s="1" t="inlineStr">
         <is>
           <t>I followed her gaze and saw Miru-chan and Rin-chan
-coming out carrying loads on both hands and shoulders.</t>
+coming out carrying loads on both hands and
+shoulders.</t>
         </is>
       </c>
       <c r="C1853" t="n">
@@ -28996,8 +29022,8 @@
       <c r="B1865" s="1" t="inlineStr">
         <is>
           <t>She seemed to be awake now, but since Rin-chan had
-been dazed all morning, Nono-chan was probably worried
-about her.</t>
+been dazed all morning, Nono-chan was probably
+worried about her.</t>
         </is>
       </c>
       <c r="C1865" t="n">
@@ -29272,8 +29298,8 @@
       </c>
       <c r="B1883" s="1" t="inlineStr">
         <is>
-          <t>「But Miru and the others get dropped off and picked up
-by bus, so that's easy~」</t>
+          <t>「But Miru and the others get dropped off and picked
+up by bus, so that's easy~」</t>
         </is>
       </c>
       <c r="C1883" t="n">
@@ -29779,8 +29805,8 @@
       </c>
       <c r="B1916" s="1" t="inlineStr">
         <is>
-          <t>Even getting off, Rurichiyo-chan was the first to step
-out.</t>
+          <t>Even getting off, Rurichiyo-chan was the first to
+step out.</t>
         </is>
       </c>
       <c r="C1916" t="n">
@@ -30531,8 +30557,8 @@
       </c>
       <c r="B1965" s="1" t="inlineStr">
         <is>
-          <t>「Miru's fine with it！ We only get to eat it sometimes,
-and Miru likes it too~！」</t>
+          <t>「Miru's fine with it！ We only get to eat it
+sometimes, and Miru likes it too~！」</t>
         </is>
       </c>
       <c r="C1965" t="n">
@@ -31129,8 +31155,9 @@
       </c>
       <c r="B2004" s="1" t="inlineStr">
         <is>
-          <t>Even though I knew it was wrong given the situation, I
-couldn't forget how good sex felt once I'd learned it.</t>
+          <t>Even though I knew it was wrong given the situation,
+I couldn't forget how good sex felt once I'd learned
+it.</t>
         </is>
       </c>
       <c r="C2004" t="n">
@@ -31527,8 +31554,8 @@
       </c>
       <c r="B2030" s="1" t="inlineStr">
         <is>
-          <t>I really love Rin-chan, but she might actually love me
-even more.</t>
+          <t>I really love Rin-chan, but she might actually love
+me even more.</t>
         </is>
       </c>
       <c r="C2030" t="n">
@@ -31989,8 +32016,8 @@
       </c>
       <c r="B2060" s="1" t="inlineStr">
         <is>
-          <t>But it's true — it's a voice I couldn't hear the first
-time.</t>
+          <t>But it's true — it's a voice I couldn't hear the
+first time.</t>
         </is>
       </c>
       <c r="C2060" t="n">
@@ -32404,8 +32431,8 @@
       </c>
       <c r="B2087" s="1" t="inlineStr">
         <is>
-          <t>Squelch, squelch — lewd, wet sounds began to rise, and
-you could tell it felt good...</t>
+          <t>Squelch, squelch — lewd, wet sounds began to rise,
+and you could tell it felt good...</t>
         </is>
       </c>
       <c r="C2087" t="n">
@@ -33125,7 +33152,8 @@
       </c>
       <c r="B2134" s="1" t="inlineStr">
         <is>
-          <t>「Fah…！ Nng, nng！ Fwaa… fuu, fuu… nng！ Nnng！ Fuu, fah…」</t>
+          <t>「Fah…！ Nng, nng！ Fwaa… fuu, fuu… nng！ Nnng！ Fuu,
+fah…」</t>
         </is>
       </c>
       <c r="C2134" t="n">
@@ -33186,8 +33214,8 @@
       </c>
       <c r="B2138" s="1" t="inlineStr">
         <is>
-          <t>She’d tense up, then exhale as she relaxed, then tense
-again… it kept repeating.</t>
+          <t>She’d tense up, then exhale as she relaxed, then
+tense again… it kept repeating.</t>
         </is>
       </c>
       <c r="C2138" t="n">
@@ -33370,8 +33398,8 @@
       <c r="B2150" s="1" t="inlineStr">
         <is>
           <t>Pulling back a little and rubbing where the glans
-catches at the narrow entrance, Rin-chan's voice burst
-out.</t>
+catches at the narrow entrance, Rin-chan's voice
+burst out.</t>
         </is>
       </c>
       <c r="C2150" t="n">
@@ -33431,7 +33459,8 @@
       </c>
       <c r="B2154" s="1" t="inlineStr">
         <is>
-          <t>「Fuaa... there, there！ Amazing—wow！ It feels so good！」</t>
+          <t>「Fuaa... there, there！ Amazing—wow！ It feels so
+good！」</t>
         </is>
       </c>
       <c r="C2154" t="n">
@@ -33766,8 +33795,8 @@
       </c>
       <c r="B2176" s="1" t="inlineStr">
         <is>
-          <t>Semen overflowing inside her vagina — Rin-chan writhes
-from that feeling.</t>
+          <t>Semen overflowing inside her vagina — Rin-chan
+writhes from that feeling.</t>
         </is>
       </c>
       <c r="C2176" t="n">
@@ -34210,7 +34239,8 @@
       </c>
       <c r="B2205" s="1" t="inlineStr">
         <is>
-          <t>As always, Rin-chan hasn't let go of my shirt and tie.</t>
+          <t>As always, Rin-chan hasn't let go of my shirt and
+tie.</t>
         </is>
       </c>
       <c r="C2205" t="n">
@@ -34396,7 +34426,8 @@
       <c r="B2217" s="1" t="inlineStr">
         <is>
           <t>Aside from Rin-chan’s cute voice, you can also hear
-loud, squelching, guchu-guchu sounds of viscous fluid.</t>
+loud, squelching, guchu-guchu sounds of viscous
+fluid.</t>
         </is>
       </c>
       <c r="C2217" t="n">
@@ -34411,9 +34442,9 @@
       </c>
       <c r="B2218" s="1" t="inlineStr">
         <is>
-          <t>Because I had already ejaculated inside once, my penis
-is crushing a blended mucus where her love juices and
-my semen are tangled together.</t>
+          <t>Because I had already ejaculated inside once, my
+penis is crushing a blended mucus where her love
+juices and my semen are tangled together.</t>
         </is>
       </c>
       <c r="C2218" t="n">
@@ -34444,9 +34475,9 @@
       </c>
       <c r="B2220" s="1" t="inlineStr">
         <is>
-          <t>When the penis moves back and forth, the blended mucus
-gets crushed at the junction and makes squelching
-sounds.</t>
+          <t>When the penis moves back and forth, the blended
+mucus gets crushed at the junction and makes
+squelching sounds.</t>
         </is>
       </c>
       <c r="C2220" t="n">
@@ -34644,9 +34675,9 @@
       </c>
       <c r="B2233" s="1" t="inlineStr">
         <is>
-          <t>The space was cramped, but depending on how you looked
-at it, we were also in a position where we could stay
-pressed together tightly.</t>
+          <t>The space was cramped, but depending on how you
+looked at it, we were also in a position where we
+could stay pressed together tightly.</t>
         </is>
       </c>
       <c r="C2233" t="n">
@@ -34865,8 +34896,8 @@
       </c>
       <c r="B2247" s="1" t="inlineStr">
         <is>
-          <t>What I just said was probably that anticipatory "feels
-good."</t>
+          <t>What I just said was probably that anticipatory
+"feels good."</t>
         </is>
       </c>
       <c r="C2247" t="n">
@@ -34926,8 +34957,8 @@
       </c>
       <c r="B2251" s="1" t="inlineStr">
         <is>
-          <t>「U-uhhnn！ Ha... ha, haa！ Niini... Niini, mo—！ It feels
-so good...！」</t>
+          <t>「U-uhhnn！ Ha... ha, haa！ Niini... Niini, mo—！ It
+feels so good...！」</t>
         </is>
       </c>
       <c r="C2251" t="n">
@@ -34974,8 +35005,8 @@
       </c>
       <c r="B2254" s="1" t="inlineStr">
         <is>
-          <t>Also, every time the penis thrusts in, the pressure on
-the blended mucus and its rebound are unbearably
+          <t>Also, every time the penis thrusts in, the pressure
+on the blended mucus and its rebound are unbearably
 delicious.</t>
         </is>
       </c>
@@ -35570,8 +35601,8 @@
       </c>
       <c r="B2293" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's breathing getting ragged, just like how the
-penis pulses when I ejaculate, is so cute.</t>
+          <t>Rin-chan's breathing getting ragged, just like how
+the penis pulses when I ejaculate, is so cute.</t>
         </is>
       </c>
       <c r="C2293" t="n">
@@ -35828,7 +35859,8 @@
       <c r="B2310" s="1" t="inlineStr">
         <is>
           <t>Rin-chan, who kept whispering 'coming, coming,'
-gradually frowned and, embarrassed, caught her breath.</t>
+gradually frowned and, embarrassed, caught her
+breath.</t>
         </is>
       </c>
       <c r="C2310" t="n">
@@ -36159,7 +36191,8 @@
       </c>
       <c r="B2332" s="1" t="inlineStr">
         <is>
-          <t>Apparently my penis was trembling without me noticing.</t>
+          <t>Apparently my penis was trembling without me
+noticing.</t>
         </is>
       </c>
       <c r="C2332" t="n">
@@ -36736,9 +36769,9 @@
       </c>
       <c r="B2370" s="1" t="inlineStr">
         <is>
-          <t>The boat was moving faster than we expected, and after
-everyone had gone out of sight we returned to the bus
-we'd parked nearby.</t>
+          <t>The boat was moving faster than we expected, and
+after everyone had gone out of sight we returned to
+the bus we'd parked nearby.</t>
         </is>
       </c>
       <c r="C2370" t="n">
@@ -36814,8 +36847,9 @@
       </c>
       <c r="B2375" s="1" t="inlineStr">
         <is>
-          <t>「Mm... well, we'll see each other again soon anyway...
-Rin staying behind alone is, um... ugh... mm.」</t>
+          <t>「Mm... well, we'll see each other again soon
+anyway... Rin staying behind alone is, um... ugh...
+mm.」</t>
         </is>
       </c>
       <c r="C2375" t="n">
@@ -36845,8 +36879,9 @@
       </c>
       <c r="B2377" s="1" t="inlineStr">
         <is>
-          <t>Though she felt bad about not seeing them off, I think
-she hated being teased for being the only one left.</t>
+          <t>Though she felt bad about not seeing them off, I
+think she hated being teased for being the only one
+left.</t>
         </is>
       </c>
       <c r="C2377" t="n">
@@ -37293,8 +37328,8 @@
       </c>
       <c r="B2406" s="1" t="inlineStr">
         <is>
-          <t>「E-even though we'll be alone in the dorm... Rin-chan,
-what do you want to do？」</t>
+          <t>「E-even though we'll be alone in the dorm...
+Rin-chan, what do you want to do？」</t>
         </is>
       </c>
       <c r="C2406" t="n">
@@ -37371,8 +37406,8 @@
       <c r="B2411" s="1" t="inlineStr">
         <is>
           <t>I wasn't expecting a particularly good answer, but
-getting such a normal reply when I was getting excited
-lets my shoulders drop.</t>
+getting such a normal reply when I was getting
+excited lets my shoulders drop.</t>
         </is>
       </c>
       <c r="C2411" t="n">
@@ -37659,8 +37694,8 @@
       </c>
       <c r="B2430" s="1" t="inlineStr">
         <is>
-          <t>Hearing Rin-chan say that, my voice accidentally flips
-over.</t>
+          <t>Hearing Rin-chan say that, my voice accidentally
+flips over.</t>
         </is>
       </c>
       <c r="C2430" t="n">
@@ -37723,8 +37758,8 @@
       </c>
       <c r="B2434" s="1" t="inlineStr">
         <is>
-          <t>Smiling wryly inside at that thought, Rin-chan made an
-even more mischievous face and said,</t>
+          <t>Smiling wryly inside at that thought, Rin-chan made
+an even more mischievous face and said,</t>
         </is>
       </c>
       <c r="C2434" t="n">

--- a/processed_ruby_restored_xlsx/sc132_凛２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc132_凛２：恋人化.ss.xlsx
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>「Ta-da—we're here！」</t>
+          <t>Ta-da—we're here！</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1086,8 +1086,8 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaahhh—！ As I thought, this place is great no
-matter when you come！」</t>
+          <t>Fwaaahhh—！ As I thought, this place is great no
+matter when you come！</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>「Heh, you must really like it here, huh.」</t>
+          <t>Heh, you must really like it here, huh.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ This place is awesome！」</t>
+          <t>Yes！ This place is awesome！</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1193,9 +1193,9 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>「…By the way, why did you decide to stop by all of a
+          <t>…By the way, why did you decide to stop by all of a
 sudden？ You said you'd be doing repairs at the dorm
-today, didn't you？」</t>
+today, didn't you？</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. Rin-chan said she wanted to stop by.」</t>
+          <t>Yeah. Rin-chan said she wanted to stop by.</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>「Huh…so, where did Rin go？」</t>
+          <t>Huh…so, where did Rin go？</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>「What！？ Rin-chan already got off？」</t>
+          <t>What！？ Rin-chan already got off？</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, she was the first one out, wasn't she？」</t>
+          <t>Yeah, she was the first one out, wasn't she？</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1378,8 +1378,8 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>「…Somehow, whenever we come here Rin-chan always
-seems to wander off on her own.」</t>
+          <t>…Somehow, whenever we come here Rin-chan always seems
+to wander off on her own.</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1409,8 +1409,8 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha…maybe it's because Rin-chan really likes this
-place too？」</t>
+          <t>Ahaha…maybe it's because Rin-chan really likes this
+place too？</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1456,8 +1456,8 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>「If it's Rin, I don't think we need to worry. She
-plays around here a lot.」</t>
+          <t>If it's Rin, I don't think we need to worry. She
+plays around here a lot.</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>「Nyaaahn！ It's Rin's, it's Rin's！」</t>
+          <t>Nyaaahn！ It's Rin's, it's Rin's！</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>「It's Rin's, so there！ Rin's！ Rin's！！」</t>
+          <t>It's Rin's, so there！ Rin's！ Rin's！！</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>W-what is going on...？</t>
+          <t>W-what is going on...？"</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>Could she have run away...！？</t>
+          <t>Could she have run away...！？"</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5728,7 +5728,7 @@
       <c r="B344" s="1" t="inlineStr">
         <is>
           <t>She left the dorm by herself while I stepped away to
-do the dishes？</t>
+do the dishes？"</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>No... that can't be... right...？</t>
+          <t>No... that can't be... right...？"</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5760,7 +5760,7 @@
         <is>
           <t>No, I don't think she'd do something like that...
 Besides, there's no way she could leave this tiny
-island anyway...</t>
+island anyway..."</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>For now, I'll ask everyone one more time.</t>
+          <t>For now, I'll ask everyone one more time."</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5791,7 +5791,7 @@
       <c r="B348" s="1" t="inlineStr">
         <is>
           <t>...When I went back to the living room, I almost
-started to tell everyone, but I held back.</t>
+started to tell everyone, but I held back."</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5807,7 +5807,7 @@
       <c r="B349" s="1" t="inlineStr">
         <is>
           <t>There's no need to go out of my way to make everyone
-worry...</t>
+worry..."</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>But if I were to ask someone about it？</t>
+          <t>But if I were to ask someone about it？"</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5838,7 +5838,7 @@
       <c r="B351" s="1" t="inlineStr">
         <is>
           <t>At times like this, it's gotta be Rurichiyo-chan,
-after all.</t>
+after all."</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama, please calm down…！」</t>
+          <t>Oji-sama, please calm down…！</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>「Rin-chan~！　Rin-chan~！？」</t>
+          <t>Rin-chan~！　Rin-chan~！？</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -7460,8 +7460,8 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>Once she got here, maybe because her nerves finally
-relaxed, she suddenly burst into tears.</t>
+          <t>Once they got here, maybe because their nerves
+finally relaxed, they suddenly burst into tears.</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -8272,8 +8272,8 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>She was probably scared... then relieved... and had
-braced herself for being scolded.</t>
+          <t>They were probably scared... then relieved... and had
+braced themselves for being scolded.</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>「Ah... um... well... you know...？」</t>
+          <t>Ah... um... well... you know...？</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>「Hm...？」</t>
+          <t>Hm...？</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="B953" s="1" t="inlineStr">
         <is>
-          <t>「Ah... sorry, what's wrong？」</t>
+          <t>Ah... sorry, what's wrong？</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B991" s="1" t="inlineStr">
         <is>
-          <t>And this time, she hurriedly pulls out a notebook.</t>
+          <t>And this time, they hurriedly pull out a notebook.</t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="B1000" s="1" t="inlineStr">
         <is>
-          <t>「…Hm？」</t>
+          <t>…Hm？</t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="B1010" s="1" t="inlineStr">
         <is>
-          <t>「Nn... phew！」</t>
+          <t>Nn... phew！</t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="B1018" s="1" t="inlineStr">
         <is>
-          <t>「………………Rin-chan！ Hey, what are you doing？」</t>
+          <t>………………Rin-chan！ Hey, what are you doing？</t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -17542,8 +17542,8 @@
       </c>
       <c r="B1116" s="1" t="inlineStr">
         <is>
-          <t>I bite my lip at my own ineptness, but the joy that
-Rin-chan put into words outweighed that.</t>
+          <t>She bites her lip at her own ineptness, but the joy
+that Rin-chan put into words outweighed that.</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -18058,7 +18058,8 @@
       </c>
       <c r="B1150" s="1" t="inlineStr">
         <is>
-          <t>Hajime</t>
+          <t>She's in the middle of kissing me, so her movements
+get a little jerky.</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -18073,7 +18074,7 @@
       </c>
       <c r="B1151" s="1" t="inlineStr">
         <is>
-          <t>「Rin-chan！ Chu！ Chu！ ...I love you！ Chu, chu！ Nchu！」</t>
+          <t>Hajime</t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -18088,7 +18089,7 @@
       </c>
       <c r="B1152" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>"Rin-chan! Chu! Chu! …I love you! Chu, chu! Nchu!"</t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -18103,7 +18104,7 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>「Aai！？ Nn... chu！ Chu！ Wa, puu... chu！ Nn, chuu...！」</t>
+          <t>Rin</t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -18118,8 +18119,7 @@
       </c>
       <c r="B1154" s="1" t="inlineStr">
         <is>
-          <t>Since she was being kissed the whole time, her words
-were coming out in little gasps.</t>
+          <t>"Aai!? Nn… chu! Chu! Wa, puu… chu! Nn, chuu…!"</t>
         </is>
       </c>
       <c r="C1154" t="n">
@@ -19144,7 +19144,7 @@
       </c>
       <c r="B1221" s="1" t="inlineStr">
         <is>
-          <t>「Huff... huffffff...」</t>
+          <t>Huff... huffffff...</t>
         </is>
       </c>
       <c r="C1221" t="n">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="B1252" s="1" t="inlineStr">
         <is>
-          <t>She agreed, didn't she...？</t>
+          <t>She agreed, didn't she...？"</t>
         </is>
       </c>
       <c r="C1252" t="n">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="B1341" s="1" t="inlineStr">
         <is>
-          <t>「…ah！」</t>
+          <t>…ah！</t>
         </is>
       </c>
       <c r="C1341" t="n">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="B1445" s="1" t="inlineStr">
         <is>
-          <t>「Nn-h！？ Ah！ Ah...！ Ah...！ Nn... ah...！？ ~~~~~~~」</t>
+          <t>「Nn-h！？ Ah！ Ah...！ Ah...！ Nn... ah...！？ ~~~~~~~"</t>
         </is>
       </c>
       <c r="C1445" t="n">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="B1447" s="1" t="inlineStr">
         <is>
-          <t>'</t>
+          <t>」</t>
         </is>
       </c>
       <c r="C1447" t="n">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="B1470" s="1" t="inlineStr">
         <is>
-          <t>「Ugh...！？ Ahh........ Ah, kah！」</t>
+          <t>Ugh...！？ Ahh........ Ah, kah！</t>
         </is>
       </c>
       <c r="C1470" t="n">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="B1501" s="1" t="inlineStr">
         <is>
-          <t>She looks like it's painful even to put it into
+          <t>They look like it's painful even to put it into
 words.</t>
         </is>
       </c>
@@ -23522,7 +23522,7 @@
       </c>
       <c r="B1507" s="1" t="inlineStr">
         <is>
-          <t>「Hey… how're you feeling right now？」</t>
+          <t>Hey… how're you feeling right now？</t>
         </is>
       </c>
       <c r="C1507" t="n">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>「Ehhhhh... Wh-what do you mean...？」</t>
+          <t>Ehhhhh... Wh-what do you mean...？</t>
         </is>
       </c>
       <c r="C1519" t="n">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="B1525" s="1" t="inlineStr">
         <is>
-          <t>「Oh... so that's how it is... I'm glad.」</t>
+          <t>Oh... so that's how it is... I'm glad.</t>
         </is>
       </c>
       <c r="C1525" t="n">
@@ -23999,8 +23999,8 @@
       </c>
       <c r="B1538" s="1" t="inlineStr">
         <is>
-          <t>Tell her clearly with words that you're not saying it
-to be mean, but because you're serious.</t>
+          <t>Tell them clearly with words that you're not saying
+it to be mean, but because you're serious.</t>
         </is>
       </c>
       <c r="C1538" t="n">
@@ -24321,8 +24321,8 @@
       </c>
       <c r="B1559" s="1" t="inlineStr">
         <is>
-          <t>With slow movements, I give a short roll of my hips,
-and Rin-chan lets out a whiny sound.</t>
+          <t>With slow movements, he gives a short roll of his
+hips, and Rin-chan lets out a whiny sound.</t>
         </is>
       </c>
       <c r="C1559" t="n">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="B1570" s="1" t="inlineStr">
         <is>
-          <t>「So does that mean your body's aching for it？」</t>
+          <t>So does that mean your body」s aching for it？</t>
         </is>
       </c>
       <c r="C1570" t="n">
@@ -24596,8 +24596,8 @@
       </c>
       <c r="B1577" s="1" t="inlineStr">
         <is>
-          <t>「Ukun！ Uwa... aa...！ There... right there, ah... it
-makes me tingle...！」</t>
+          <t>Ukun！ Uwa... aa...！ There... right there, ah... it
+makes me tingle...！</t>
         </is>
       </c>
       <c r="C1577" t="n">
@@ -26527,8 +26527,8 @@
       </c>
       <c r="B1703" s="1" t="inlineStr">
         <is>
-          <t>I can't believe I'm feeling good because I cum inside
-me...</t>
+          <t>I can't believe I'm feeling good because he cum
+inside me...</t>
         </is>
       </c>
       <c r="C1703" t="n">
@@ -26618,8 +26618,8 @@
       </c>
       <c r="B1709" s="1" t="inlineStr">
         <is>
-          <t>Her vagina filled with my cum, and I drove it home
-with my words — she's so small, and yet she's really
+          <t>My vagina filled with his cum, and he drove it home
+with his words — I'm so small, and yet I'm really
 coming...</t>
         </is>
       </c>
@@ -26771,8 +26771,8 @@
       </c>
       <c r="B1719" s="1" t="inlineStr">
         <is>
-          <t>When I said it again to try it, sure enough her
-vagina clenched.</t>
+          <t>When I said it again to try it, sure enough my vagina
+clenched.</t>
         </is>
       </c>
       <c r="C1719" t="n">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="B1749" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan felt good too, right...？</t>
+          <t>Rin-chan felt good too, right...？"</t>
         </is>
       </c>
       <c r="C1749" t="n">
@@ -29099,7 +29099,7 @@
       </c>
       <c r="B1870" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei？ That's not okay...！」</t>
+          <t>Janitor-sensei？ That's not okay...！</t>
         </is>
       </c>
       <c r="C1870" t="n">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="B1929" s="1" t="inlineStr">
         <is>
-          <t>「Um—Janitor-sensei？」</t>
+          <t>Um—Janitor-sensei？</t>
         </is>
       </c>
       <c r="C1929" t="n">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="B1995" s="1" t="inlineStr">
         <is>
-          <t>「R-Rin-chan... wake up, shall we eat lunch？」</t>
+          <t>R-Rin-chan... wake up, shall we eat lunch？</t>
         </is>
       </c>
       <c r="C1995" t="n">
@@ -31295,8 +31295,8 @@
       </c>
       <c r="B2013" s="1" t="inlineStr">
         <is>
-          <t>As I mumble, Rin-chan looks back at me with a lonely
-expression.</t>
+          <t>As he mumbles, Rin-chan looks back at me with a
+lonely expression.</t>
         </is>
       </c>
       <c r="C2013" t="n">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="B2054" s="1" t="inlineStr">
         <is>
-          <t>Her face was trembling too, and yet she grabbed my
+          <t>Their face was trembling too, and yet they grabbed my
 tie.</t>
         </is>
       </c>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="B2080" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... nngh, nnhit！ Hyaaah？」</t>
+          <t>Nnngh... nngh, nnhit！ Hyaaah？</t>
         </is>
       </c>
       <c r="C2080" t="n">
@@ -32661,8 +32661,8 @@
       </c>
       <c r="B2102" s="1" t="inlineStr">
         <is>
-          <t>「Nnn...！ Ah... yaa... nn！ Fuu, uuh！ N-aaah... afu,
-nnn...！」</t>
+          <t>Nnn...！ Ah... yaa... nn！ Fuu, uuh！ N-aaah... afu,
+nnn...！</t>
         </is>
       </c>
       <c r="C2102" t="n">
@@ -32754,8 +32754,8 @@
       </c>
       <c r="B2108" s="1" t="inlineStr">
         <is>
-          <t>「Yah... w-wait！ S-something's... wrong... Hah...
-h-huh！ Ah！」</t>
+          <t>Yah... w-wait！ S-something's... wrong... Hah...
+h-huh！ Ah！</t>
         </is>
       </c>
       <c r="C2108" t="n">
@@ -32861,7 +32861,7 @@
       </c>
       <c r="B2115" s="1" t="inlineStr">
         <is>
-          <t>Growling, I pushed me away with one hand.</t>
+          <t>Growling, he pushed me away with one hand.</t>
         </is>
       </c>
       <c r="C2115" t="n">
@@ -32952,7 +32952,7 @@
       </c>
       <c r="B2121" s="1" t="inlineStr">
         <is>
-          <t>Then Rin-chan, keeping the hand that was pushing me
+          <t>Then Rin-chan, keeping the hand that was pushing him
 away in place, tugs on the tie she’s grabbed with her
 other hand.</t>
         </is>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="B2122" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C2122" t="n">
@@ -33045,7 +33045,7 @@
       </c>
       <c r="B2127" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C2127" t="n">
@@ -33137,7 +33137,7 @@
       </c>
       <c r="B2133" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C2133" t="n">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="B2142" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C2142" t="n">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="B2148" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C2148" t="n">
@@ -33903,7 +33903,7 @@
       <c r="B2183" s="1" t="inlineStr">
         <is>
           <t>Rin-chan doesn't know the embarrassment of a guy who
-came sooner than I expected.</t>
+came sooner than he expected.</t>
         </is>
       </c>
       <c r="C2183" t="n">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="B2214" s="1" t="inlineStr">
         <is>
-          <t>「Ah—no！ Hah, hauuu！ Hyaa... aaah！ Ugh... un！」</t>
+          <t>Ah—no！ Hah, hauuu！ Hyaa... aaah！ Ugh... un！</t>
         </is>
       </c>
       <c r="C2214" t="n">
@@ -34442,9 +34442,9 @@
       </c>
       <c r="B2218" s="1" t="inlineStr">
         <is>
-          <t>Because I had already ejaculated inside once, my
+          <t>Because he had already ejaculated inside once, his
 penis is crushing a blended mucus where her love
-juices and my semen are tangled together.</t>
+juices and his semen are tangled together.</t>
         </is>
       </c>
       <c r="C2218" t="n">
@@ -35053,7 +35053,7 @@
       </c>
       <c r="B2257" s="1" t="inlineStr">
         <is>
-          <t>「Fuaa！ Fuaaaah！ Noo... nooo...！ Rin, not... ahhh...！」</t>
+          <t>Fuaa！ Fuaaaah！ Noo... nooo...！ Rin, not... ahhh...！</t>
         </is>
       </c>
       <c r="C2257" t="n">
@@ -35783,7 +35783,7 @@
       </c>
       <c r="B2305" s="1" t="inlineStr">
         <is>
-          <t>「Uh—yeah… it feels good… all the time, okay？」</t>
+          <t>Uh—yeah… it feels good… all the time, okay？</t>
         </is>
       </c>
       <c r="C2305" t="n">
@@ -36586,8 +36586,8 @@
       </c>
       <c r="B2358" s="1" t="inlineStr">
         <is>
-          <t>To fill that loneliness first, we shared a long, long
-kiss...</t>
+          <t>To fill that loneliness first, they shared a long,
+long kiss...</t>
         </is>
       </c>
       <c r="C2358" t="n">
